--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.76.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.76.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.76.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.76.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="49" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -605,16 +605,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L53: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of a traversing note : orâ€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]e</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]e</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L4: symbol-only separator/garbage line :: , 835:</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L6: symbol-only separator/garbage line :: ,835.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]e</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -666,16 +670,8 @@
           <t>L27: line starts with digit/letter garbage token | suspicious token(s): 6been (letter/digit mix) :: 6been</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: order for leave to amend : orâ€”â€”</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L52: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: after the date of the order for leave to amend: orâ€” amend.</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -685,7 +681,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L20: isolated marker/symbol line :: &gt;</t>
+          <t>L6: symbol-only separator/garbage line :: ,835.</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -725,22 +721,18 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L81: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: re a subp Ã¦ na to hear judgment</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L53: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: i</t>
+          <t>L20: isolated marker/symbol line :: &gt;</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -762,12 +754,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -785,7 +777,11 @@
           <t>L57: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L73: isolated marker/symbol line :: i</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
@@ -965,12 +961,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1009,7 +1005,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1048,7 +1044,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
